--- a/Libraries/Vehicle/Dampers/Damper/sm_car_data_Damper_Linear.xlsx
+++ b/Libraries/Vehicle/Dampers/Damper/sm_car_data_Damper_Linear.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Dampers\Damper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SMILLER\TMW\Sharepoint\PM_Evl\sscMbody\2024\2409_VDGUP\Models_and_Files\Proj1\CAD_251201_New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAC1278-0785-4727-91D1-EC67994AC00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288BED08-058F-447D-8FC4-9FD5FCB7D643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29805" yWindow="3375" windowWidth="21600" windowHeight="11235" tabRatio="967" firstSheet="9" activeTab="17" xr2:uid="{C5A4D212-38D5-4645-961A-DE2D82DDDABE}"/>
+    <workbookView xWindow="31050" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="967" firstSheet="7" activeTab="10" xr2:uid="{C5A4D212-38D5-4645-961A-DE2D82DDDABE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_HambaLG_f" sheetId="1" r:id="rId1"/>
@@ -2086,14 +2086,13 @@
         <v>43</v>
       </c>
       <c r="F6" s="21">
-        <f>2.8-2.79</f>
-        <v>9.9999999999997868E-3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G6" s="21">
-        <v>0.48549999999999999</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="H6" s="21">
-        <v>0.67633500000000002</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="J6" s="13" t="s">
         <v>43</v>
@@ -2115,14 +2114,13 @@
         <v>43</v>
       </c>
       <c r="F7" s="21">
-        <f>2.8-2.79</f>
-        <v>9.9999999999997868E-3</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="G7" s="21">
-        <v>0.48549999999999999</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="H7" s="21">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="J7" s="13" t="s">
         <v>43</v>
@@ -2148,7 +2146,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="18">
-        <v>0.13500000000000001</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="J8" s="14" t="s">
         <v>43</v>
@@ -2169,7 +2167,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="18">
-        <v>-0.115</v>
+        <v>-0.158</v>
       </c>
       <c r="J9" s="14" t="s">
         <v>43</v>
@@ -9002,13 +9000,13 @@
         <v>43</v>
       </c>
       <c r="F6" s="21">
-        <v>-1.5900000000000001E-2</v>
+        <v>-1.7000000000000001E-2</v>
       </c>
       <c r="G6" s="21">
-        <v>0.50453999999999999</v>
+        <v>0.48399999999999999</v>
       </c>
       <c r="H6" s="21">
-        <v>0.62</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="J6" s="13" t="s">
         <v>43</v>
@@ -9030,13 +9028,13 @@
         <v>43</v>
       </c>
       <c r="F7" s="21">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="G7" s="21">
-        <v>0.50453999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="H7" s="21">
-        <v>0.5</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="J7" s="13" t="s">
         <v>43</v>

--- a/Libraries/Vehicle/Dampers/Damper/sm_car_data_Damper_Linear.xlsx
+++ b/Libraries/Vehicle/Dampers/Damper/sm_car_data_Damper_Linear.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4716CE18-76AF-4225-884A-1C814229B2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8130" yWindow="2010" windowWidth="21945" windowHeight="13260" tabRatio="967" xr2:uid="{C5A4D212-38D5-4645-961A-DE2D82DDDABE}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="967" firstSheet="4" activeTab="12" xr2:uid="{C5A4D212-38D5-4645-961A-DE2D82DDDABE}"/>
   </bookViews>
   <sheets>
     <sheet name="None" sheetId="28" r:id="rId1"/>
@@ -1545,12 +1545,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A9:B12">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:A14">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1840,22 +1840,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="77" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="76" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="75" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="74" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2143,22 +2143,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="73" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="72" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="71" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="70" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2448,22 +2448,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="69" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="68" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="67" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="66" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2752,22 +2752,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="65" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="64" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="63" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="62" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3056,22 +3056,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="61" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="60" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="59" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="58" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3359,22 +3359,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="57" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="56" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="54" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3662,22 +3662,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="53" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="52" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="51" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="50" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3965,22 +3965,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="48" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="47" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4268,22 +4268,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="45" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="44" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="43" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="42" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4572,22 +4572,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="41" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="40" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="39" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4723,12 +4723,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A9:B12">
-    <cfRule type="cellIs" dxfId="107" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:A14">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5017,22 +5017,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="36" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="35" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5314,22 +5314,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="30" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5611,22 +5611,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="28" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="26" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5910,22 +5910,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6209,22 +6209,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6508,22 +6508,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6808,22 +6808,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7108,22 +7108,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7407,22 +7407,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7704,22 +7704,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="104" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="103" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="102" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8001,22 +8001,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="101" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="100" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="99" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="98" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8298,22 +8298,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="97" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="96" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="95" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="94" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8595,22 +8595,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="93" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="92" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="91" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="90" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8892,22 +8892,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="89" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="88" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="87" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="86" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9197,22 +9197,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="85" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="83" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="82" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9496,22 +9496,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="cellIs" dxfId="81" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
-    <cfRule type="cellIs" dxfId="80" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:B14">
-    <cfRule type="cellIs" dxfId="79" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B7">
-    <cfRule type="cellIs" dxfId="78" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
